--- a/product_selector_out/STM8L151-152 - diff.xlsx
+++ b/product_selector_out/STM8L151-152 - diff.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>864</v>
+        <v>891</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>864</v>
+        <v>891</v>
       </c>
     </row>
     <row r="18">
